--- a/Excel/8. Advance Filters/Data+Tools.xlsx
+++ b/Excel/8. Advance Filters/Data+Tools.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Advance_Excel_BI\8. Advance Filters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_04\Excel\8. Advance Filters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F474BA7F-124B-4210-974C-68D32FA7DA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573130E9-F02F-4A8B-AF83-8246A80A99BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sorting" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Data Validations'!$H$4:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Data Validations'!$H$4:$K$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Filtering!$H$4:$N$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Remove Duplicates'!$H$4:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Text to column'!$H$4:$K$10</definedName>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t>Example</t>
   </si>
@@ -217,16 +217,12 @@
   </si>
   <si>
     <t xml:space="preserve"> ALT + A +T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72
-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -342,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -499,21 +495,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -604,9 +591,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -622,7 +606,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{69011797-AF4F-497D-88CE-607A6FDF0438}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1496,23 +1482,23 @@
       <c r="D1" s="2"/>
       <c r="E1" s="8"/>
       <c r="F1" s="14"/>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
       <c r="V1" s="13"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1668,53 +1654,53 @@
     <row r="13" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D13" s="25"/>
       <c r="H13" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" s="20">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="J13" s="24"/>
     </row>
     <row r="14" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H14" s="20" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I14" s="20">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H15" s="20" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I15" s="20">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H16" s="20" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I16" s="20">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
       <c r="H17" s="20" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I17" s="20">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="H18" s="20" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="20">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1722,7 +1708,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H13:I18">
-    <sortCondition ref="H13:H18"/>
+    <sortCondition descending="1" ref="H13:H18"/>
   </sortState>
   <mergeCells count="6">
     <mergeCell ref="T1:U1"/>
@@ -1762,23 +1748,23 @@
       <c r="D1" s="2"/>
       <c r="E1" s="8"/>
       <c r="F1" s="14"/>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
       <c r="V1" s="13"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1815,7 +1801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="E5" s="11"/>
       <c r="F5" s="17"/>
@@ -1845,7 +1831,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="34">
         <v>1</v>
       </c>
@@ -1909,7 +1895,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="35">
         <v>3</v>
       </c>
@@ -1941,7 +1927,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36">
         <v>4</v>
       </c>
@@ -2006,9 +1992,10 @@
     </row>
   </sheetData>
   <autoFilter ref="H4:N9" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="4">
+    <filterColumn colId="1">
       <filters>
-        <filter val="B"/>
+        <filter val="99"/>
+        <filter val="100"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2049,22 +2036,22 @@
       <c r="D1" s="2"/>
       <c r="E1" s="8"/>
       <c r="F1" s="14"/>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
       <c r="K1" s="13"/>
       <c r="L1" s="13"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
       <c r="U1" s="13"/>
     </row>
     <row r="2" spans="1:21" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2094,8 +2081,8 @@
       <c r="K4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="L4" t="s">
-        <v>4</v>
+      <c r="L4" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>2</v>
@@ -2118,9 +2105,7 @@
       <c r="K5" s="21">
         <v>85</v>
       </c>
-      <c r="L5" s="40">
-        <v>95</v>
-      </c>
+      <c r="L5" s="21"/>
       <c r="N5" s="33" t="s">
         <v>3</v>
       </c>
@@ -2144,6 +2129,7 @@
       <c r="K6" s="21">
         <v>43</v>
       </c>
+      <c r="L6" s="21"/>
       <c r="N6" s="33" t="s">
         <v>4</v>
       </c>
@@ -2167,6 +2153,7 @@
       <c r="K7" s="21">
         <v>79</v>
       </c>
+      <c r="L7" s="21"/>
       <c r="N7" s="33" t="s">
         <v>10</v>
       </c>
@@ -2190,6 +2177,7 @@
       <c r="K8" s="21">
         <v>82</v>
       </c>
+      <c r="L8" s="21"/>
       <c r="N8" s="33" t="s">
         <v>41</v>
       </c>
@@ -2213,6 +2201,7 @@
       <c r="K9" s="21">
         <v>30</v>
       </c>
+      <c r="L9" s="21"/>
       <c r="N9" s="33" t="s">
         <v>13</v>
       </c>
@@ -2232,6 +2221,7 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
       <c r="N10" s="33" t="s">
         <v>14</v>
       </c>
@@ -2263,7 +2253,7 @@
       <c r="B19" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="H4:L10" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="H4:K10" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="5">
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="G1:J1"/>
@@ -2279,12 +2269,12 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Kindly put values between 0 - 95." prompt="_x000a_" sqref="L5" xr:uid="{DB5867FC-9F67-4321-84DD-BDF0301ABBD5}">
-      <formula1>0</formula1>
-      <formula2>98</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4" xr:uid="{C5055E89-EC2D-46DA-A572-A13D31F7DCCD}">
+      <formula1>$N$7:$N$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4" xr:uid="{020EEFE4-FBC1-4B26-BE6D-154085E5FF55}">
-      <formula1>$N$4:$N$10</formula1>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Something Went Wrong" error="You need to check the message before entering." promptTitle="Fill the details" prompt="Please enter a value between 35 and 95." sqref="L5:L10" xr:uid="{42A911D5-8BBF-4870-9E9D-DDAC857AC16A}">
+      <formula1>35</formula1>
+      <formula2>95</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2316,23 +2306,23 @@
       <c r="D1" s="2"/>
       <c r="E1" s="8"/>
       <c r="F1" s="14"/>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
       <c r="V1" s="13"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2467,7 +2457,7 @@
     </row>
     <row r="11" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D11" s="25"/>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="40" t="s">
         <v>12</v>
       </c>
       <c r="I11" s="21">
@@ -2482,7 +2472,7 @@
     </row>
     <row r="12" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D12" s="25"/>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="40" t="s">
         <v>45</v>
       </c>
       <c r="I12" s="21">
@@ -2491,8 +2481,8 @@
       <c r="J12" s="21">
         <v>63</v>
       </c>
-      <c r="K12" s="42" t="s">
-        <v>53</v>
+      <c r="K12" s="41">
+        <v>72</v>
       </c>
       <c r="L12" s="21"/>
     </row>
@@ -2559,24 +2549,24 @@
       <c r="D1" s="2"/>
       <c r="E1" s="8"/>
       <c r="F1" s="14"/>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
       <c r="L1" s="13"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
       <c r="W1" s="13"/>
     </row>
     <row r="2" spans="1:23" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
